--- a/data/publications.xlsx
+++ b/data/publications.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jitendra/Git Projects/CV_JITENDRA_2026/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git Projects\jitendrakv.github.io\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0E0D25D-E3DE-C24B-AB9F-5511FC815F34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7361D98-5200-4A9C-AC43-1D2447B9CC0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="33600" windowHeight="20400" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Books" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="674" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="668" uniqueCount="415">
   <si>
     <t>Authors</t>
   </si>
@@ -972,12 +972,6 @@
     <t>A Forensic Multi-Omics Framework for Robust Breast Cancer Biomarker Discovery Using Explainable AI and Network Biology</t>
   </si>
   <si>
-    <t>Collaborative Learning Enabled Workload Prediction Model for Large-Scale Cloud Environments</t>
-  </si>
-  <si>
-    <t>TENCON 2026, Indonesia</t>
-  </si>
-  <si>
     <t>Accepted for presentation</t>
   </si>
   <si>
@@ -1285,6 +1279,9 @@
   </si>
   <si>
     <t>International Conference on Artificial Intelligence and Networking 2026, UAE</t>
+  </si>
+  <si>
+    <t>Rimsha Alam, Usha Chouhan, Abhinav Gupta, Jitendra Kumar</t>
   </si>
 </sst>
 </file>
@@ -1341,7 +1338,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1367,58 +1364,11 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="14">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF545245"/>
-          <bgColor rgb="FF545245"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1648,6 +1598,50 @@
       </font>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF545245"/>
+          <bgColor rgb="FF545245"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1662,21 +1656,21 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4B03D7DB-CBB2-704E-A0C0-B18023175DBF}" name="Table1" displayName="Table1" ref="A1:L38" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4B03D7DB-CBB2-704E-A0C0-B18023175DBF}" name="Table1" displayName="Table1" ref="A1:L38" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
   <autoFilter ref="A1:L38" xr:uid="{4B03D7DB-CBB2-704E-A0C0-B18023175DBF}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{3B12948C-2157-0E4B-9C55-4202CEA73C98}" name="Authors" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{0EBECD1F-436B-9747-ADC7-2F318F0B3336}" name="Title" dataDxfId="12"/>
-    <tableColumn id="3" xr3:uid="{4C2A9310-309A-554F-9EFC-46C3AD787044}" name="Journal" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{C8D21A12-BB3F-9140-8E96-FFAFEA7B3E73}" name="Volume" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{38FB8441-E2C0-3F41-B098-E70A0785E209}" name="Year" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{B53FFD38-6759-624D-BC00-C3A6307D1AF3}" name="PageStart" dataDxfId="8"/>
-    <tableColumn id="7" xr3:uid="{76AC494B-8BF5-4D47-856B-4E416BB6B234}" name="PageEnd" dataDxfId="7"/>
-    <tableColumn id="8" xr3:uid="{B0A6FEE4-84A0-6F4C-8ABC-8F8C94E4EA3B}" name="Indexing" dataDxfId="6"/>
-    <tableColumn id="9" xr3:uid="{F18A905A-1E07-BC4F-B9A9-6FFC6A642C54}" name="Quartile" dataDxfId="5"/>
-    <tableColumn id="10" xr3:uid="{7EE7992C-08D0-644C-ADCA-2059072958D0}" name="ImpactFactor" dataDxfId="4"/>
-    <tableColumn id="11" xr3:uid="{00134AE0-A8CE-9240-9E80-546182B2E9B5}" name="Status" dataDxfId="3"/>
-    <tableColumn id="12" xr3:uid="{F04E22BF-5BB7-3546-B43F-E4CA19958693}" name="URL" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{3B12948C-2157-0E4B-9C55-4202CEA73C98}" name="Authors" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{0EBECD1F-436B-9747-ADC7-2F318F0B3336}" name="Title" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{4C2A9310-309A-554F-9EFC-46C3AD787044}" name="Journal" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{C8D21A12-BB3F-9140-8E96-FFAFEA7B3E73}" name="Volume" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{38FB8441-E2C0-3F41-B098-E70A0785E209}" name="Year" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{B53FFD38-6759-624D-BC00-C3A6307D1AF3}" name="PageStart" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{76AC494B-8BF5-4D47-856B-4E416BB6B234}" name="PageEnd" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{B0A6FEE4-84A0-6F4C-8ABC-8F8C94E4EA3B}" name="Indexing" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{F18A905A-1E07-BC4F-B9A9-6FFC6A642C54}" name="Quartile" dataDxfId="3"/>
+    <tableColumn id="10" xr3:uid="{7EE7992C-08D0-644C-ADCA-2059072958D0}" name="ImpactFactor" dataDxfId="2"/>
+    <tableColumn id="11" xr3:uid="{00134AE0-A8CE-9240-9E80-546182B2E9B5}" name="Status" dataDxfId="1"/>
+    <tableColumn id="12" xr3:uid="{F04E22BF-5BB7-3546-B43F-E4CA19958693}" name="URL" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1968,7 +1962,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
     <col min="2" max="2" width="45" customWidth="1"/>
@@ -1980,7 +1974,7 @@
     <col min="10" max="10" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2012,7 +2006,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="56" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" ht="51" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -2040,7 +2034,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="56" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>18</v>
       </c>
@@ -2068,7 +2062,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="70" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>25</v>
       </c>
@@ -2096,7 +2090,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="84" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>30</v>
       </c>
@@ -2132,7 +2126,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:J5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
     <col min="2" max="2" width="45" customWidth="1"/>
@@ -2144,7 +2138,7 @@
     <col min="10" max="10" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2176,7 +2170,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="28" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>39</v>
       </c>
@@ -2200,7 +2194,7 @@
       </c>
       <c r="J2" s="2"/>
     </row>
-    <row r="3" spans="1:10" ht="70" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>45</v>
       </c>
@@ -2230,7 +2224,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="84" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>51</v>
       </c>
@@ -2260,7 +2254,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="84" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>56</v>
       </c>
@@ -2298,7 +2292,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:L38"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
     <col min="2" max="2" width="45" customWidth="1"/>
@@ -2306,15 +2300,15 @@
     <col min="4" max="4" width="12" style="5" customWidth="1"/>
     <col min="5" max="5" width="8" style="5" customWidth="1"/>
     <col min="6" max="6" width="12" style="5" customWidth="1"/>
-    <col min="7" max="7" width="11.33203125" style="5" customWidth="1"/>
+    <col min="7" max="7" width="11.28515625" style="5" customWidth="1"/>
     <col min="8" max="8" width="14" style="5" customWidth="1"/>
-    <col min="9" max="9" width="10.5" style="5" customWidth="1"/>
-    <col min="10" max="10" width="15.1640625" style="7" customWidth="1"/>
+    <col min="9" max="9" width="10.42578125" style="5" customWidth="1"/>
+    <col min="10" max="10" width="15.140625" style="7" customWidth="1"/>
     <col min="11" max="11" width="20" style="5" customWidth="1"/>
     <col min="12" max="12" width="30" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2352,7 +2346,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="28" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>65</v>
       </c>
@@ -2378,7 +2372,7 @@
       <c r="I2" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="J2" s="9">
+      <c r="J2" s="4">
         <v>4.9000000000000004</v>
       </c>
       <c r="K2" s="4" t="s">
@@ -2388,7 +2382,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="28" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>65</v>
       </c>
@@ -2414,7 +2408,7 @@
       <c r="I3" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="J3" s="4" t="s">
         <v>77</v>
       </c>
       <c r="K3" s="4" t="s">
@@ -2424,7 +2418,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="42" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>79</v>
       </c>
@@ -2462,7 +2456,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>87</v>
       </c>
@@ -2496,7 +2490,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>94</v>
       </c>
@@ -2534,7 +2528,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>102</v>
       </c>
@@ -2570,7 +2564,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="28" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>108</v>
       </c>
@@ -2602,7 +2596,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="70" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>115</v>
       </c>
@@ -2640,7 +2634,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>123</v>
       </c>
@@ -2678,7 +2672,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>131</v>
       </c>
@@ -2716,7 +2710,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="28" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>138</v>
       </c>
@@ -2754,7 +2748,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>138</v>
       </c>
@@ -2788,7 +2782,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>150</v>
       </c>
@@ -2826,7 +2820,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="28" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>159</v>
       </c>
@@ -2864,7 +2858,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="28" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>167</v>
       </c>
@@ -2902,7 +2896,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="28" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>175</v>
       </c>
@@ -2938,7 +2932,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="42" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>182</v>
       </c>
@@ -2976,7 +2970,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="28" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>190</v>
       </c>
@@ -3014,7 +3008,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="28" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>196</v>
       </c>
@@ -3052,7 +3046,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="28" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>196</v>
       </c>
@@ -3090,7 +3084,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="28" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>175</v>
       </c>
@@ -3128,7 +3122,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="28" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>217</v>
       </c>
@@ -3166,7 +3160,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="28" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>225</v>
       </c>
@@ -3204,7 +3198,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="28" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>175</v>
       </c>
@@ -3242,7 +3236,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="28" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>175</v>
       </c>
@@ -3280,7 +3274,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="42" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>175</v>
       </c>
@@ -3318,7 +3312,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="28" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>253</v>
       </c>
@@ -3356,7 +3350,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="28" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>175</v>
       </c>
@@ -3390,7 +3384,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="28" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>175</v>
       </c>
@@ -3428,7 +3422,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="42" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>276</v>
       </c>
@@ -3462,7 +3456,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="42" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>284</v>
       </c>
@@ -3488,7 +3482,7 @@
       </c>
       <c r="L32" s="4"/>
     </row>
-    <row r="33" spans="1:12" ht="42" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>288</v>
       </c>
@@ -3514,7 +3508,7 @@
       </c>
       <c r="L33" s="4"/>
     </row>
-    <row r="34" spans="1:12" ht="42" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:12" ht="51" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>291</v>
       </c>
@@ -3540,7 +3534,7 @@
       </c>
       <c r="L34" s="4"/>
     </row>
-    <row r="35" spans="1:12" ht="42" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:12" ht="51" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>295</v>
       </c>
@@ -3566,7 +3560,7 @@
       </c>
       <c r="L35" s="4"/>
     </row>
-    <row r="36" spans="1:12" ht="42" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>138</v>
       </c>
@@ -3592,7 +3586,7 @@
       </c>
       <c r="L36" s="4"/>
     </row>
-    <row r="37" spans="1:12" ht="42" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>301</v>
       </c>
@@ -3618,7 +3612,7 @@
       </c>
       <c r="L37" s="4"/>
     </row>
-    <row r="38" spans="1:12" ht="42" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>305</v>
       </c>
@@ -3654,8 +3648,8 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:J20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:J19"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
     <col min="2" max="2" width="45" customWidth="1"/>
@@ -3668,7 +3662,7 @@
     <col min="10" max="10" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3700,15 +3694,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="42" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>284</v>
+        <v>414</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>310</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>43</v>
@@ -3719,20 +3713,20 @@
         <v>113</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
     </row>
-    <row r="3" spans="1:10" ht="28" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>39</v>
+        <v>312</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>43</v>
@@ -3743,53 +3737,59 @@
         <v>113</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
     </row>
-    <row r="4" spans="1:10" ht="42" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>314</v>
+        <v>138</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
+        <v>27</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>319</v>
+      </c>
       <c r="G4" s="4" t="s">
         <v>113</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>317</v>
+        <v>49</v>
       </c>
       <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-    </row>
-    <row r="5" spans="1:10" ht="42" x14ac:dyDescent="0.2">
+      <c r="J4" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>138</v>
+        <v>322</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>27</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>113</v>
@@ -3799,27 +3799,27 @@
       </c>
       <c r="I5" s="2"/>
       <c r="J5" s="2" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="42" x14ac:dyDescent="0.2">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>27</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>113</v>
@@ -3829,27 +3829,27 @@
       </c>
       <c r="I6" s="2"/>
       <c r="J6" s="2" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="42" x14ac:dyDescent="0.2">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>27</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>331</v>
+        <v>270</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>113</v>
@@ -3857,29 +3857,31 @@
       <c r="H7" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="I7" s="2"/>
+      <c r="I7" s="2" t="s">
+        <v>335</v>
+      </c>
       <c r="J7" s="2" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="42" x14ac:dyDescent="0.2">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>27</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>270</v>
+        <v>339</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>113</v>
@@ -3887,46 +3889,36 @@
       <c r="H8" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="I8" s="2" t="s">
-        <v>337</v>
-      </c>
+      <c r="I8" s="2"/>
       <c r="J8" s="2" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="42" x14ac:dyDescent="0.2">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="51" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>323</v>
+        <v>344</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E9" s="4" t="s">
-        <v>341</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>342</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>113</v>
-      </c>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
       <c r="H9" s="2" t="s">
-        <v>49</v>
+        <v>315</v>
       </c>
       <c r="I9" s="2"/>
-      <c r="J9" s="2" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="42" x14ac:dyDescent="0.2">
+      <c r="J9" s="2"/>
+    </row>
+    <row r="10" spans="1:10" ht="51" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>344</v>
+        <v>138</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>345</v>
@@ -3935,35 +3927,43 @@
         <v>346</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
+        <v>154</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>113</v>
+      </c>
       <c r="H10" s="2" t="s">
-        <v>317</v>
+        <v>49</v>
       </c>
       <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-    </row>
-    <row r="11" spans="1:10" ht="56" x14ac:dyDescent="0.2">
+      <c r="J10" s="2" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>138</v>
+        <v>350</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>154</v>
+        <v>21</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>350</v>
+        <v>48</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>113</v>
@@ -3973,27 +3973,27 @@
       </c>
       <c r="I11" s="2"/>
       <c r="J11" s="2" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="28" x14ac:dyDescent="0.2">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>352</v>
+        <v>175</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>21</v>
+        <v>357</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>355</v>
+        <v>47</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>48</v>
+        <v>147</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>113</v>
@@ -4001,29 +4001,31 @@
       <c r="H12" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="I12" s="2"/>
+      <c r="I12" s="2" t="s">
+        <v>358</v>
+      </c>
       <c r="J12" s="2" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="42" x14ac:dyDescent="0.2">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>175</v>
+        <v>360</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="D13" s="4" t="s">
         <v>357</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>359</v>
-      </c>
       <c r="E13" s="4" t="s">
-        <v>47</v>
+        <v>363</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>147</v>
+        <v>364</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>113</v>
@@ -4031,31 +4033,29 @@
       <c r="H13" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="I13" s="2" t="s">
-        <v>360</v>
-      </c>
+      <c r="I13" s="2"/>
       <c r="J13" s="2" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="42" x14ac:dyDescent="0.2">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="51" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>113</v>
@@ -4065,27 +4065,27 @@
       </c>
       <c r="I14" s="2"/>
       <c r="J14" s="2" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="56" x14ac:dyDescent="0.2">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="G15" s="4" t="s">
         <v>113</v>
@@ -4095,27 +4095,27 @@
       </c>
       <c r="I15" s="2"/>
       <c r="J15" s="2" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="42" x14ac:dyDescent="0.2">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>374</v>
+        <v>175</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>364</v>
+        <v>378</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>359</v>
+        <v>379</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>376</v>
+        <v>230</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="G16" s="4" t="s">
         <v>113</v>
@@ -4123,29 +4123,31 @@
       <c r="H16" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="I16" s="2"/>
+      <c r="I16" s="2" t="s">
+        <v>358</v>
+      </c>
       <c r="J16" s="2" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="42" x14ac:dyDescent="0.2">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>175</v>
+        <v>382</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>230</v>
+        <v>386</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="G17" s="4" t="s">
         <v>113</v>
@@ -4153,31 +4155,29 @@
       <c r="H17" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="I17" s="2" t="s">
-        <v>360</v>
-      </c>
+      <c r="I17" s="2"/>
       <c r="J17" s="2" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="42" x14ac:dyDescent="0.2">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="D18" s="4" t="s">
         <v>385</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>387</v>
-      </c>
       <c r="E18" s="4" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>113</v>
@@ -4187,27 +4187,27 @@
       </c>
       <c r="I18" s="2"/>
       <c r="J18" s="2" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="42" x14ac:dyDescent="0.2">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>387</v>
+        <v>398</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>394</v>
+        <v>47</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>113</v>
@@ -4217,37 +4217,7 @@
       </c>
       <c r="I19" s="2"/>
       <c r="J19" s="2" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="28" x14ac:dyDescent="0.2">
-      <c r="A20" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="D20" s="4" t="s">
         <v>400</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>401</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2" t="s">
-        <v>402</v>
       </c>
     </row>
   </sheetData>
@@ -4258,7 +4228,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:F4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
     <col min="2" max="2" width="45" customWidth="1"/>
@@ -4268,7 +4238,7 @@
     <col min="6" max="6" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4276,7 +4246,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>4</v>
@@ -4288,58 +4258,58 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="28" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>109</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>21</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>406</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" ht="42" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>407</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>409</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>410</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="28" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>411</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>413</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
   </sheetData>
